--- a/SAEN PEÑA/Octubre/SAENZ_EXPENSAS-Octubre.xlsx
+++ b/SAEN PEÑA/Octubre/SAENZ_EXPENSAS-Octubre.xlsx
@@ -5,28 +5,28 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCD4499-420B-4E86-A694-D3A7E291CEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7831841E-FF16-420E-AC41-75843587D663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
-    <sheet name="extraordinaria" sheetId="4" r:id="rId3"/>
-    <sheet name="prorrateo  (2)" sheetId="5" r:id="rId4"/>
+    <sheet name="prorrateo  (2)" sheetId="5" r:id="rId3"/>
+    <sheet name="extraordinaria" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="81">
   <si>
     <t>UF</t>
   </si>
@@ -238,24 +238,52 @@
     <t>PRESUPUESTO APROBADO - MANO DE OBRA GAS Y CLOACAS</t>
   </si>
   <si>
-    <t>Liquidacion mes de SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Período SEPTIEMBRE </t>
+    <t>Liquidacion mes de OCTUBRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Período OCTUBRE </t>
+  </si>
+  <si>
+    <t>Ladrisur - Arena, ladrillos, cemento</t>
+  </si>
+  <si>
+    <t>Matafuegos Fire - Recarga de matafuegos, manguera ABC p/ polvo - Cambio de marbete/precinto - P/ hidraulica matafuegos/ pres. manuales</t>
+  </si>
+  <si>
+    <t>Julio Doartero - cambio de llave de gas vereda - Materiales y mano de obra</t>
+  </si>
+  <si>
+    <t>Diferencia materiales (instalacion de gas)</t>
+  </si>
+  <si>
+    <t>Transportes villar - Camion 27/09</t>
+  </si>
+  <si>
+    <t>Banchero Sanitarios Sa - compra acople</t>
+  </si>
+  <si>
+    <t>Banchero Sanitarios Sa - compra cupla, buje, codos varios, sellador, teflon</t>
+  </si>
+  <si>
+    <t>Ingeso de extraordinarias</t>
+  </si>
+  <si>
+    <t>Egreso de extraordinarias Sr. Julio Doartero - Resta abonar $500.000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,13 +385,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
@@ -1059,7 +1080,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1131,7 +1152,6 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1164,7 +1184,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="10" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1178,7 +1197,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1241,12 +1259,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1269,12 +1283,18 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="14" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="14" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1332,6 +1352,19 @@
     <xf numFmtId="167" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1699,7 +1732,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1719,7 +1752,7 @@
       <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="97" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1748,12 +1781,12 @@
         <v>43</v>
       </c>
       <c r="B7" s="24"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
       <c r="E7" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="101"/>
+      <c r="F7" s="98"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
@@ -1769,122 +1802,130 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="104" t="s">
+      <c r="A11" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="100"/>
+      <c r="B11" s="97"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="126" t="s">
+      <c r="E11" s="121" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="126"/>
+      <c r="F11" s="121"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="102"/>
-      <c r="B12" s="102"/>
-      <c r="C12" s="110"/>
+      <c r="A12" s="99"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="144"/>
       <c r="D12" s="5"/>
       <c r="E12" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="49">
-        <v>890833.31141901179</v>
+      <c r="F12" s="143">
+        <v>1355249.5529328201</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="100" t="s">
+      <c r="A13" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="100" t="s">
+      <c r="B13" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="109">
+      <c r="C13" s="144">
         <v>35601</v>
       </c>
       <c r="D13" s="36"/>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="50">
         <f>'prorrateo '!F11</f>
-        <v>646382.94151380809</v>
+        <v>125902.75973000002</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="102" t="s">
+      <c r="A14" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="109">
-        <v>27930.06</v>
+      <c r="C14" s="144">
+        <v>31704.36</v>
       </c>
       <c r="D14" s="5"/>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="51">
-        <f>-(C35)</f>
-        <v>-181966.7</v>
+      <c r="F14" s="50">
+        <f>-(C42)</f>
+        <v>-1710814.9800000002</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="100" t="s">
+      <c r="B15" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="73">
+      <c r="C15" s="145">
         <v>32800</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="51"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="100"/>
-      <c r="B16" s="100"/>
-      <c r="C16" s="73"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="51"/>
+      <c r="E15" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="50">
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="97"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="145"/>
+      <c r="E16" s="148" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="50">
+        <v>-4000000</v>
+      </c>
       <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="105"/>
-      <c r="B17" s="106"/>
-      <c r="C17" s="80">
+      <c r="A17" s="102"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="146">
         <f>SUM(C12:C16)</f>
-        <v>96331.06</v>
-      </c>
-      <c r="E17" s="52" t="s">
+        <v>100105.36</v>
+      </c>
+      <c r="E17" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="125">
+      <c r="F17" s="118">
         <f>SUM(F12:F16)</f>
-        <v>1355249.5529328201</v>
+        <v>270337.33266281988</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="104" t="s">
+      <c r="A18" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="100"/>
-      <c r="C18" s="107"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="147"/>
       <c r="D18" s="5"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="100" t="s">
+      <c r="A19" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="108" t="s">
+      <c r="B19" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="73">
+      <c r="C19" s="145">
         <f xml:space="preserve"> 56588+56588*3%</f>
         <v>58285.64</v>
       </c>
@@ -1892,211 +1933,294 @@
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="100" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="108"/>
-      <c r="C20" s="109">
-        <v>27350</v>
+    <row r="20" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="122" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="123"/>
+      <c r="C20" s="145">
+        <v>45399.98</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="100" t="s">
-        <v>67</v>
-      </c>
-      <c r="B21" s="108"/>
-      <c r="C21" s="109"/>
+    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="97" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="104"/>
+      <c r="C21" s="145">
+        <v>635000</v>
+      </c>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="105"/>
-      <c r="B22" s="106"/>
-      <c r="C22" s="123">
-        <f>SUM(C18:C21)</f>
-        <v>85635.64</v>
+    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="104"/>
+      <c r="C22" s="145">
+        <v>118270</v>
       </c>
       <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="124">
-        <f>+C22+C17</f>
-        <v>181966.7</v>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="97" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="104"/>
+      <c r="C23" s="145">
+        <v>3918.62</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="75"/>
-      <c r="C24" s="76"/>
+    <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="97" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="104"/>
+      <c r="C24" s="145">
+        <v>176142.38</v>
+      </c>
+      <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
+    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="97" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="104"/>
+      <c r="C25" s="145">
+        <v>363693</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20"/>
+    </row>
+    <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="97" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="104"/>
+      <c r="C26" s="144">
+        <v>210000</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
+    </row>
+    <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="97" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="104"/>
+      <c r="C27" s="144"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="20"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="97" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="104"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="102"/>
+      <c r="B29" s="103"/>
+      <c r="C29" s="119">
+        <f>SUM(C18:C28)</f>
+        <v>1610709.62</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="41"/>
+      <c r="C30" s="120">
+        <f>+C29+C17</f>
+        <v>1710814.9800000002</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="20"/>
+    </row>
+    <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="60" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="37"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="46"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="45">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="53"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="45">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="71"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="74"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="71"/>
-      <c r="B30" s="78"/>
-      <c r="C30" s="79"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="71"/>
-      <c r="B31" s="77"/>
-      <c r="C31" s="74">
-        <v>0</v>
-      </c>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="55" t="s">
+      <c r="B31" s="73"/>
+      <c r="C31" s="74"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="20"/>
+    </row>
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="37"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="46"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="44"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="45">
+        <v>0</v>
+      </c>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="52"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="45">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="69"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="72"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="69"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="77"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="69"/>
+      <c r="B38" s="75"/>
+      <c r="C38" s="72">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="56"/>
-      <c r="C32" s="57">
-        <f>SUM(C27:C31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B39" s="55"/>
+      <c r="C39" s="56">
+        <f>SUM(C34:C38)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="45">
-        <f>C23-C21</f>
-        <v>181966.7</v>
-      </c>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="C40" s="149">
+        <f>C30-C28</f>
+        <v>1710814.9800000002</v>
+      </c>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="70">
-        <f>+C23</f>
-        <v>181966.7</v>
-      </c>
-      <c r="E34" s="103"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="55" t="s">
+      <c r="C41" s="150">
+        <f>+C30</f>
+        <v>1710814.9800000002</v>
+      </c>
+      <c r="E41" s="100"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="56"/>
-      <c r="C35" s="57">
-        <f>C33</f>
-        <v>181966.7</v>
-      </c>
-      <c r="E35" s="16"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D42" s="16"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="151">
+        <f>C40</f>
+        <v>1710814.9800000002</v>
+      </c>
       <c r="E42" s="16"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D43" s="16"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D44" s="16"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="19"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="20"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="18"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="18"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="18"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="18"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="18"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="18"/>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D50" s="16"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D51" s="16"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="19"/>
       <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
+      <c r="C63" s="20"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2132,11 +2256,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
       <c r="D1" s="26"/>
       <c r="E1" s="25" t="s">
         <v>41</v>
@@ -2148,29 +2272,29 @@
       <c r="H1" s="26"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
-      <c r="K1" s="63">
-        <v>181966.7</v>
+      <c r="K1" s="62">
+        <v>1710814.9800000002</v>
       </c>
       <c r="L1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="str">
+      <c r="A2" s="63" t="str">
         <f>'detalle y gastos'!E7</f>
-        <v>Liquidacion mes de SEPTIEMBRE</v>
-      </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67" t="s">
+        <v>Liquidacion mes de OCTUBRE</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="69"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="68"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -2236,7 +2360,7 @@
       <c r="K4" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="58" t="s">
+      <c r="L4" s="57" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2254,26 +2378,23 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>174994.10772580802</v>
-      </c>
-      <c r="F5" s="73">
-        <f>E5</f>
-        <v>174994.10772580802</v>
-      </c>
-      <c r="G5" s="59">
+        <v>27513.365040000001</v>
+      </c>
+      <c r="F5" s="71"/>
+      <c r="G5" s="58">
         <f>E5-F5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="62">
+        <v>27513.365040000001</v>
+      </c>
+      <c r="H5" s="61">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>0</v>
+        <v>2311.1226633600004</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="31">
         <f>K1*D5</f>
-        <v>27513.365040000001</v>
+        <v>258675.22497600003</v>
       </c>
       <c r="K5" s="15">
         <f>K2*D5</f>
@@ -2281,7 +2402,7 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>27513.365040000001</v>
+        <v>288499.71267936</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -2298,26 +2419,23 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>87135.848281500002</v>
-      </c>
-      <c r="F6" s="73">
-        <f t="shared" ref="F6:F10" si="0">E6</f>
-        <v>87135.848281500002</v>
-      </c>
-      <c r="G6" s="59">
-        <f t="shared" ref="G6:G8" si="1">E6-F6</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="62">
-        <f t="shared" ref="H6:H10" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>0</v>
+        <v>28550.575230000002</v>
+      </c>
+      <c r="F6" s="71"/>
+      <c r="G6" s="58">
+        <f t="shared" ref="G6:G8" si="0">E6-F6</f>
+        <v>28550.575230000002</v>
+      </c>
+      <c r="H6" s="61">
+        <f t="shared" ref="H6:H10" si="1">IF(G6&gt;0,G6*8.4%,0)</f>
+        <v>2398.2483193200005</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
       </c>
       <c r="J6" s="31">
         <f>K1*D6</f>
-        <v>28550.575230000002</v>
+        <v>268426.87036200007</v>
       </c>
       <c r="K6" s="15">
         <f>K2*D6</f>
@@ -2325,7 +2443,7 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>28550.575230000002</v>
+        <v>299375.69391132006</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -2342,18 +2460,18 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>87857.815157000005</v>
-      </c>
-      <c r="F7" s="73">
+        <v>28787.131940000003</v>
+      </c>
+      <c r="F7" s="71">
+        <f t="shared" ref="F6:F10" si="2">E7</f>
+        <v>28787.131940000003</v>
+      </c>
+      <c r="G7" s="58">
         <f t="shared" si="0"/>
-        <v>87857.815157000005</v>
-      </c>
-      <c r="G7" s="59">
+        <v>0</v>
+      </c>
+      <c r="H7" s="61">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="62">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I7" s="15">
@@ -2361,7 +2479,7 @@
       </c>
       <c r="J7" s="31">
         <f>K1*D7</f>
-        <v>28787.131940000003</v>
+        <v>270650.92983600002</v>
       </c>
       <c r="K7" s="15">
         <f>K2*D7</f>
@@ -2369,7 +2487,7 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="3">J7+K7+H7+G7</f>
-        <v>28787.131940000003</v>
+        <v>270650.92983600002</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2386,18 +2504,18 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="E8" s="34">
-        <v>109961.10873000001</v>
-      </c>
-      <c r="F8" s="73">
+        <v>36029.406600000002</v>
+      </c>
+      <c r="F8" s="71">
+        <f t="shared" si="2"/>
+        <v>36029.406600000002</v>
+      </c>
+      <c r="G8" s="58">
         <f t="shared" si="0"/>
-        <v>109961.10873000001</v>
-      </c>
-      <c r="G8" s="59">
+        <v>0</v>
+      </c>
+      <c r="H8" s="61">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="62">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I8" s="15">
@@ -2405,7 +2523,7 @@
       </c>
       <c r="J8" s="31">
         <f>K1*D8</f>
-        <v>36029.406600000002</v>
+        <v>338741.36604000005</v>
       </c>
       <c r="K8" s="15">
         <f>K2*D8</f>
@@ -2413,7 +2531,7 @@
       </c>
       <c r="L8" s="32">
         <f t="shared" si="3"/>
-        <v>36029.406600000002</v>
+        <v>338741.36604000005</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2430,18 +2548,18 @@
         <v>0.15920000000000001</v>
       </c>
       <c r="E9" s="34">
-        <v>88413.174292000011</v>
-      </c>
-      <c r="F9" s="73">
-        <f t="shared" si="0"/>
-        <v>88413.174292000011</v>
-      </c>
-      <c r="G9" s="59">
+        <v>28969.098640000004</v>
+      </c>
+      <c r="F9" s="71">
+        <f t="shared" si="2"/>
+        <v>28969.098640000004</v>
+      </c>
+      <c r="G9" s="58">
         <f>E9-F9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="62">
-        <f t="shared" si="2"/>
+      <c r="H9" s="61">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" s="15">
@@ -2449,7 +2567,7 @@
       </c>
       <c r="J9" s="31">
         <f>K1*D9</f>
-        <v>28969.098640000004</v>
+        <v>272361.74481600005</v>
       </c>
       <c r="K9" s="15">
         <f>K2*D9</f>
@@ -2457,7 +2575,7 @@
       </c>
       <c r="L9" s="32">
         <f t="shared" si="3"/>
-        <v>28969.098640000004</v>
+        <v>272361.74481600005</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -2474,18 +2592,18 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>98020.887327499993</v>
-      </c>
-      <c r="F10" s="73">
-        <f t="shared" si="0"/>
-        <v>98020.887327499993</v>
-      </c>
-      <c r="G10" s="59">
+        <v>32117.12255</v>
+      </c>
+      <c r="F10" s="71">
+        <f t="shared" si="2"/>
+        <v>32117.12255</v>
+      </c>
+      <c r="G10" s="58">
         <f>E10-F10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="62">
-        <f t="shared" si="2"/>
+      <c r="H10" s="61">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I10" s="15">
@@ -2493,7 +2611,7 @@
       </c>
       <c r="J10" s="31">
         <f>K1*D10</f>
-        <v>32117.12255</v>
+        <v>301958.84397000005</v>
       </c>
       <c r="K10" s="15">
         <f>K2*D10</f>
@@ -2501,7 +2619,7 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>32117.12255</v>
+        <v>301958.84397000005</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2516,19 +2634,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="4">SUM(E5:E10)</f>
-        <v>646382.94151380809</v>
+        <v>181966.7</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>646382.94151380809</v>
+        <v>125902.75973000002</v>
       </c>
       <c r="G11" s="42">
         <f>SUM(G5:G10)</f>
-        <v>0</v>
+        <v>56063.940270000006</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" ref="H11:K11" si="5">SUM(H5:H10)</f>
-        <v>0</v>
+        <v>4709.3709826800005</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="5"/>
@@ -2536,7 +2654,7 @@
       </c>
       <c r="J11" s="39">
         <f t="shared" si="5"/>
-        <v>181966.7</v>
+        <v>1710814.9800000002</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="5"/>
@@ -2544,22 +2662,22 @@
       </c>
       <c r="L11" s="42">
         <f>SUM(L5:L10)</f>
-        <v>181966.7</v>
+        <v>1771588.2912526804</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="127"/>
-      <c r="B12" s="127"/>
-      <c r="C12" s="127"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="127"/>
-      <c r="K12" s="127"/>
-      <c r="L12" s="127"/>
+      <c r="A12" s="124"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="124"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="124"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
@@ -2579,255 +2697,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="133" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="136" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="137"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="139">
-        <v>565</v>
-      </c>
-      <c r="E2" s="140"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="141" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="141" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="141" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="143" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="128" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="128" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="128" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="142"/>
-      <c r="B4" s="142"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="144"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="83">
-        <v>1</v>
-      </c>
-      <c r="B5" s="85" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="86" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="84">
-        <v>0.1512</v>
-      </c>
-      <c r="E5" s="87">
-        <v>85</v>
-      </c>
-      <c r="F5" s="87">
-        <v>0</v>
-      </c>
-      <c r="G5" s="87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="83">
-        <v>2</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="86" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="84">
-        <v>0.15690000000000001</v>
-      </c>
-      <c r="E6" s="87">
-        <v>89</v>
-      </c>
-      <c r="F6" s="87">
-        <v>0</v>
-      </c>
-      <c r="G6" s="87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="83">
-        <v>3</v>
-      </c>
-      <c r="B7" s="85" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="84">
-        <v>0.15820000000000001</v>
-      </c>
-      <c r="E7" s="87">
-        <v>89</v>
-      </c>
-      <c r="F7" s="87">
-        <v>0</v>
-      </c>
-      <c r="G7" s="87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="83">
-        <v>4</v>
-      </c>
-      <c r="B8" s="85" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="97" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="84">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="E8" s="87">
-        <v>112</v>
-      </c>
-      <c r="F8" s="87">
-        <v>0</v>
-      </c>
-      <c r="G8" s="87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="83">
-        <v>5</v>
-      </c>
-      <c r="B9" s="85" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="86" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="84">
-        <v>0.15920000000000001</v>
-      </c>
-      <c r="E9" s="87">
-        <v>90</v>
-      </c>
-      <c r="F9" s="87">
-        <v>0</v>
-      </c>
-      <c r="G9" s="87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88">
-        <v>6</v>
-      </c>
-      <c r="B10" s="90" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="91" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="89">
-        <v>0.17649999999999999</v>
-      </c>
-      <c r="E10" s="92">
-        <v>100</v>
-      </c>
-      <c r="F10" s="92">
-        <v>0</v>
-      </c>
-      <c r="G10" s="92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="93" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="94"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="95">
-        <v>1</v>
-      </c>
-      <c r="E11" s="95">
-        <v>565</v>
-      </c>
-      <c r="F11" s="95" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="96" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="130"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="132"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0B7803-3483-4F5E-AF3D-BAA45E718D12}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2848,19 +2717,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="145">
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="142">
         <v>4500000</v>
       </c>
-      <c r="H1" s="145"/>
-      <c r="I1" s="115"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="110"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
@@ -2922,16 +2791,16 @@
       <c r="C4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="116">
+      <c r="D4" s="111">
         <v>0.1512</v>
       </c>
       <c r="E4" s="34">
         <v>0</v>
       </c>
-      <c r="F4" s="73">
-        <v>0</v>
-      </c>
-      <c r="G4" s="117">
+      <c r="F4" s="71">
+        <v>0</v>
+      </c>
+      <c r="G4" s="112">
         <f>E4-F4</f>
         <v>0</v>
       </c>
@@ -2954,16 +2823,16 @@
       <c r="C5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="116">
+      <c r="D5" s="111">
         <v>0.15690000000000001</v>
       </c>
       <c r="E5" s="34">
         <v>0</v>
       </c>
-      <c r="F5" s="73">
-        <v>0</v>
-      </c>
-      <c r="G5" s="117">
+      <c r="F5" s="71">
+        <v>0</v>
+      </c>
+      <c r="G5" s="112">
         <f t="shared" ref="G5:G7" si="1">E5-F5</f>
         <v>0</v>
       </c>
@@ -2986,16 +2855,16 @@
       <c r="C6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="116">
+      <c r="D6" s="111">
         <v>0.15820000000000001</v>
       </c>
       <c r="E6" s="34">
         <v>0</v>
       </c>
-      <c r="F6" s="73">
-        <v>0</v>
-      </c>
-      <c r="G6" s="117">
+      <c r="F6" s="71">
+        <v>0</v>
+      </c>
+      <c r="G6" s="112">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3018,16 +2887,16 @@
       <c r="C7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="116">
+      <c r="D7" s="111">
         <v>0.19800000000000001</v>
       </c>
       <c r="E7" s="34">
         <v>0</v>
       </c>
-      <c r="F7" s="73">
-        <v>0</v>
-      </c>
-      <c r="G7" s="117">
+      <c r="F7" s="71">
+        <v>0</v>
+      </c>
+      <c r="G7" s="112">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3050,16 +2919,16 @@
       <c r="C8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="116">
+      <c r="D8" s="111">
         <v>0.15920000000000001</v>
       </c>
       <c r="E8" s="34">
         <v>0</v>
       </c>
-      <c r="F8" s="73">
-        <v>0</v>
-      </c>
-      <c r="G8" s="117">
+      <c r="F8" s="71">
+        <v>0</v>
+      </c>
+      <c r="G8" s="112">
         <f>E8-F8</f>
         <v>0</v>
       </c>
@@ -3082,16 +2951,16 @@
       <c r="C9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="116">
+      <c r="D9" s="111">
         <v>0.17649999999999999</v>
       </c>
       <c r="E9" s="34">
         <v>0</v>
       </c>
-      <c r="F9" s="73">
-        <v>0</v>
-      </c>
-      <c r="G9" s="117">
+      <c r="F9" s="71">
+        <v>0</v>
+      </c>
+      <c r="G9" s="112">
         <f>E9-F9</f>
         <v>0</v>
       </c>
@@ -3105,12 +2974,12 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="121">
+      <c r="B10" s="114"/>
+      <c r="C10" s="115"/>
+      <c r="D10" s="116">
         <f>SUM(D4:D9)</f>
         <v>1</v>
       </c>
@@ -3126,7 +2995,7 @@
         <f>SUM(G4:G9)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="122">
+      <c r="H10" s="117">
         <f t="shared" ref="H10" si="4">SUM(H4:H9)</f>
         <v>4500000</v>
       </c>
@@ -3136,15 +3005,15 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="127"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I12" s="6"/>
@@ -3162,4 +3031,253 @@
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="133" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136">
+        <v>565</v>
+      </c>
+      <c r="E2" s="137"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="138" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="138" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="140" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="125" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="125" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="125" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="139"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="80">
+        <v>1</v>
+      </c>
+      <c r="B5" s="82" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="83" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="81">
+        <v>0.1512</v>
+      </c>
+      <c r="E5" s="84">
+        <v>85</v>
+      </c>
+      <c r="F5" s="84">
+        <v>0</v>
+      </c>
+      <c r="G5" s="84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="80">
+        <v>2</v>
+      </c>
+      <c r="B6" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="81">
+        <v>0.15690000000000001</v>
+      </c>
+      <c r="E6" s="84">
+        <v>89</v>
+      </c>
+      <c r="F6" s="84">
+        <v>0</v>
+      </c>
+      <c r="G6" s="84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="80">
+        <v>3</v>
+      </c>
+      <c r="B7" s="82" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="81">
+        <v>0.15820000000000001</v>
+      </c>
+      <c r="E7" s="84">
+        <v>89</v>
+      </c>
+      <c r="F7" s="84">
+        <v>0</v>
+      </c>
+      <c r="G7" s="84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="80">
+        <v>4</v>
+      </c>
+      <c r="B8" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="81">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="E8" s="84">
+        <v>112</v>
+      </c>
+      <c r="F8" s="84">
+        <v>0</v>
+      </c>
+      <c r="G8" s="84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="80">
+        <v>5</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="83" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="81">
+        <v>0.15920000000000001</v>
+      </c>
+      <c r="E9" s="84">
+        <v>90</v>
+      </c>
+      <c r="F9" s="84">
+        <v>0</v>
+      </c>
+      <c r="G9" s="84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="85">
+        <v>6</v>
+      </c>
+      <c r="B10" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="88" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="86">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="E10" s="89">
+        <v>100</v>
+      </c>
+      <c r="F10" s="89">
+        <v>0</v>
+      </c>
+      <c r="G10" s="89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="90" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="92">
+        <v>1</v>
+      </c>
+      <c r="E11" s="92">
+        <v>565</v>
+      </c>
+      <c r="F11" s="92" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="93" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="127"/>
+      <c r="B12" s="128"/>
+      <c r="C12" s="128"/>
+      <c r="D12" s="128"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>